--- a/scripts/product_upload_template_v1.xlsx
+++ b/scripts/product_upload_template_v1.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B61F0F21-3002-9748-9668-E5C0C31ABB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Products" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Data" state="hidden" r:id="rId5"/>
+    <sheet name="Products" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -389,14 +391,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -438,12 +440,307 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M46"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -525,7 +822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -566,7 +863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -607,7 +904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -648,7 +945,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -689,7 +986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -730,7 +1027,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -771,7 +1068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -812,7 +1109,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -853,7 +1150,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -894,7 +1191,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -935,7 +1232,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -976,7 +1273,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1314,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1058,7 +1355,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1099,7 +1396,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1140,7 +1437,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -1181,7 +1478,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -1222,7 +1519,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1263,7 +1560,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1304,7 +1601,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -1345,7 +1642,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -1386,7 +1683,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -1427,7 +1724,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>67</v>
       </c>
@@ -1468,7 +1765,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -1509,7 +1806,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -1550,7 +1847,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -1591,7 +1888,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>73</v>
       </c>
@@ -1632,7 +1929,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1673,7 +1970,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1714,7 +2011,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -1755,7 +2052,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -1796,7 +2093,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1837,7 +2134,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>83</v>
       </c>
@@ -1878,7 +2175,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1919,7 +2216,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>87</v>
       </c>
@@ -1960,7 +2257,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>88</v>
       </c>
@@ -2001,7 +2298,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -2042,7 +2339,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2083,7 +2380,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -2124,7 +2421,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2165,7 +2462,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -2206,7 +2503,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -2247,7 +2544,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -2288,7 +2585,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -2330,30 +2627,34 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F10:F1001">
-      <formula1>Data!$A$2:$A$13</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F1001">
-      <formula1>Data!$A$2:$A$13</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M10:M1001">
-      <formula1>Data!$B$2:$B$31</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M1001">
-      <formula1>Data!$B$2:$B$31</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>Data!$A$2:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F1001</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>Data!$B$2:$B$31</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1001</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>104</v>
       </c>
@@ -2361,7 +2662,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>106</v>
       </c>
@@ -2369,7 +2670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>107</v>
       </c>
@@ -2377,7 +2678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>108</v>
       </c>
@@ -2385,7 +2686,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>110</v>
       </c>
@@ -2393,7 +2694,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -2401,7 +2702,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>112</v>
       </c>
@@ -2409,7 +2710,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -2417,7 +2718,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -2425,7 +2726,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>115</v>
       </c>
@@ -2433,7 +2734,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2441,7 +2742,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>116</v>
       </c>
@@ -2449,7 +2750,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>117</v>
       </c>
@@ -2457,92 +2758,92 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>122</v>
       </c>
